--- a/output/260721__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260721__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00999999"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -80,6 +85,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -476,96 +482,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] [단독] 이재명표 ‘공공 의대’ 최소 967억…위치는 이곳 가능성</t>
+          <t>[연합뉴스TV] 다시 거세진 장맛비…수도권 출근길 '물폭탄' 주의보 [7월 21일 AI PICK]</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003538911?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/422/0000887028?sid=100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 비당권파 시·도당위원장 대거 포진… 장동혁 ‘우군’이 없다</t>
+          <t>[YTN] 정점식-이준석 오찬 회동...대여투쟁 공조 논의 전망</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662717?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002382094?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 선고 하루 앞 오세훈 '정치 운명' 공방 격화…시정·대권 행보 기로</t>
+          <t>[서울신문] 여야, 원 구성은 뒷전… 종합특검 연장법 상정에 ‘필버’ 충돌</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009069297?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003662718?sid=100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 김민석 “반명 분열주의 심판해야”… 정청래 “집토끼 나가면 총선 불...</t>
+          <t>[중앙일보] “씰 데 없는 소리 하고 있어!” YS 욱하게 한 초선 MB 질문</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735255?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003538908?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] 국힘 윤리위, 주중 회의 연다… 장동혁發 '징계 내전' 본격화</t>
+          <t>[뉴스1] '종합특검 연장법' 오늘 국회 통과 전망…野 필리버스터, 與 종결 대응</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005388317?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009069322?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] “가치실종” vs “주류의식”… 순혈주의에 숨막힌 이재명의 길</t>
+          <t>[노컷뉴스] "오롯이 시민의 마음으로"…장정순 용인시의회 의장의 '시민 정치'</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/005/0001862096?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/079/0004170142?sid=102</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[문화일보] ‘호남 민심’ 구애 나선 김민석 아내 이태린 여사</t>
+          <t>[동아일보] 후반기 국회 시작부터 충돌… 민주 “특검 연장” 국힘 ‘필버’ 맞불</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/021/0002805798?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735258?sid=100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[YTN] 첫 합동연설회서 '표심 전쟁'...정청래 집중 견제</t>
+          <t>[머니투데이] 원구성도 못한채 강대강 대치… 후반기 첫 본회의부터 '필버'</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002382075?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005388302?sid=100</t>
         </is>
       </c>
     </row>
@@ -577,196 +583,90 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>[경향신문] [단독]잠실 시위 현장 업무에 ‘긴급 심리지원’ 받은 경찰 19명…법적...</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003459333?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>[경향신문] [속보]‘관저 이전 조작 감사’ 유병호 구속···법원 “증거인멸 염려...</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/032/0003459327?sid=102</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>[연합뉴스TV] 리얼미터 "이 대통령 지지도 48.4%…소폭 하락"</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/422/0000887036?sid=100</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>[노컷뉴스] 수사권 폐지해도 남는 '檢기소독점'…독일의 견제장치는?</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004170139?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>[연합뉴스] 與, '보완수사권 폐지' 놓고 전문가 정책의총…"논의 심화"</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/001/0016204711?sid=100</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>3) 국민의힘 동정</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>[이데일리] [속보]뉴욕증시 또 하락…'중동 불안'에 빅테크 실적 경계감까지</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/018/0006333457?sid=101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] [단독] 종합특검, '관저 사전답사' 김건희·윤한홍·21그램 동선 포착…...</t>
+          <t>[디지털타임스] 美 42개 주서 ‘AI 데이터 센터’ 반대 시위…“전기·물 사용량 높여 부...</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000943376?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003037916?sid=101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] 오세훈, 부동산 대토론회 참석 불발…김용범 회동으로 갈음</t>
+          <t>[이데일리] 중동 전운에 숨죽인 뉴욕증시…빅테크 실적 시즌 '시험대' [월스트리트...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004170138?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006333472?sid=101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[세계일보] 李, 분당 아파트 매각… 野 “17억 근저당 꼼수거래”</t>
+          <t>[이데일리] "AI 투자 증가세 꺾여"…"성장률 둔화와 피크아웃 구분해야"</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/022/0004144547?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/018/0006333461?sid=101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 꺼지지 않는 신용대출 증가세…"고점 물린 개미들, 상환 여유도 없어"</t>
+          <t>[서울경제] AI 투자 경쟁의 그림자…미국 빅테크 ‘숨은 빚’ 2455조원</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009069329?sid=101</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>[한국일보] "대구 핵심시설 품은 도시철도 4호선... 재검토는 다각도로, 추진은 속도...</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000943387?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>4) 경제 동정</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>[서울신문] [단독] 경찰 ‘순환인사 확대’ 반발 확산… 직협, 집회·수사경과 반납...</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662721?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>[한국일보] [단독] '쿠팡이츠'서 온 팀장님, 전 회사 자료로 '땡겨요' 만들었나</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/469/0000943384?sid=102</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>[동아일보] [단독]주력사업 부진에… 돈 안되는 ‘미래 먹거리’ 손턴다</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735202?sid=101</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>[뉴시스] "지금 안 사면 늦는다"…전세난이 키운 서울 집값 악순환</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014077149?sid=101</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>[머니투데이] '저가 공세' 중국 보고 있나...AI 올라탄 'K철강', 수출액 들썩</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005388350?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004643324?sid=104</t>
         </is>
       </c>
     </row>

--- a/output/260721__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260721__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -482,96 +482,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[연합뉴스TV] 다시 거세진 장맛비…수도권 출근길 '물폭탄' 주의보 [7월 21일 AI PICK]</t>
+          <t>[YTN] 정점식-이준석 오찬 회동...대여투쟁 공조 논의 전망</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/422/0000887028?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002382094?sid=100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[YTN] 정점식-이준석 오찬 회동...대여투쟁 공조 논의 전망</t>
+          <t>[서울신문] 여야, 원 구성은 뒷전… 종합특검 연장법 상정에 ‘필버’ 충돌</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002382094?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/081/0003662718?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 여야, 원 구성은 뒷전… 종합특검 연장법 상정에 ‘필버’ 충돌</t>
+          <t>[중앙일보] “씰 데 없는 소리 하고 있어!” YS 욱하게 한 초선 MB 질문</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662718?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/025/0003538908?sid=100</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] “씰 데 없는 소리 하고 있어!” YS 욱하게 한 초선 MB 질문</t>
+          <t>[뉴스1] '종합특검 연장법' 오늘 국회 통과 전망…野 필리버스터, 與 종결 대응</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003538908?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/421/0009069322?sid=100</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] '종합특검 연장법' 오늘 국회 통과 전망…野 필리버스터, 與 종결 대응</t>
+          <t>[동아일보] 후반기 국회 시작부터 충돌… 민주 “특검 연장” 국힘 ‘필버’ 맞불</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009069322?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/020/0003735258?sid=100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[노컷뉴스] "오롯이 시민의 마음으로"…장정순 용인시의회 의장의 '시민 정치'</t>
+          <t>[머니투데이] 원구성도 못한채 강대강 대치… 후반기 첫 본회의부터 '필버'</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/079/0004170142?sid=102</t>
+          <t>https://n.news.naver.com/mnews/article/008/0005388302?sid=100</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 후반기 국회 시작부터 충돌… 민주 “특검 연장” 국힘 ‘필버’ 맞불</t>
+          <t>[YTN] 종합특검 연장법 '필버' 대치...오늘 통과 불투명?</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735258?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/052/0002382121?sid=100</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] 원구성도 못한채 강대강 대치… 후반기 첫 본회의부터 '필버'</t>
+          <t>[서울경제] [기자의 눈] 단일종목 레버리지가 소환한 ‘라임의 추억’</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005388302?sid=100</t>
+          <t>https://n.news.naver.com/mnews/article/011/0004643312?sid=101</t>
         </is>
       </c>
     </row>
@@ -625,48 +625,48 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[디지털타임스] 美 42개 주서 ‘AI 데이터 센터’ 반대 시위…“전기·물 사용량 높여 부...</t>
+          <t>[뉴시스] 1500원대 무너진 원·달러…强달러 여지는 '여전'</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003037916?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014077136?sid=101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[이데일리] 중동 전운에 숨죽인 뉴욕증시…빅테크 실적 시즌 '시험대' [월스트리트...</t>
+          <t>[뉴시스] 日서 먼저 오른 아이폰값…'200만원 아이폰' 한국도 눈앞</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006333472?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014077151?sid=105</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[이데일리] "AI 투자 증가세 꺾여"…"성장률 둔화와 피크아웃 구분해야"</t>
+          <t>[디지털타임스] 美 42개 주서 ‘AI 데이터 센터’ 반대 시위…“전기·물 사용량 높여 부...</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006333461?sid=101</t>
+          <t>https://n.news.naver.com/mnews/article/029/0003037916?sid=101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[서울경제] AI 투자 경쟁의 그림자…미국 빅테크 ‘숨은 빚’ 2455조원</t>
+          <t>[뉴시스] V자 반등 기대했는데 'L자' 늪?…다시 떠오르는 '박스피' 우려</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004643324?sid=104</t>
+          <t>https://n.news.naver.com/mnews/article/003/0014077142?sid=101</t>
         </is>
       </c>
     </row>

--- a/output/260721__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260721__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002382094?sid=100</t>
+          <t>https://tinyurl.com/27dn77nr</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/081/0003662718?sid=100</t>
+          <t>https://tinyurl.com/29uxej5u</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/025/0003538908?sid=100</t>
+          <t>https://tinyurl.com/2cryc5yh</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/421/0009069322?sid=100</t>
+          <t>https://tinyurl.com/2xlpprzn</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/020/0003735258?sid=100</t>
+          <t>https://tinyurl.com/2yg769co</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/008/0005388302?sid=100</t>
+          <t>https://tinyurl.com/2y2ggyw7</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/052/0002382121?sid=100</t>
+          <t>https://tinyurl.com/2623uotd</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/011/0004643312?sid=101</t>
+          <t>https://tinyurl.com/27h4dyan</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/018/0006333457?sid=101</t>
+          <t>https://tinyurl.com/28bzqg4o</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014077136?sid=101</t>
+          <t>https://tinyurl.com/27us38o7</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014077151?sid=105</t>
+          <t>https://tinyurl.com/223q84xx</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/029/0003037916?sid=101</t>
+          <t>https://tinyurl.com/23uqr7ht</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/mnews/article/003/0014077142?sid=101</t>
+          <t>https://tinyurl.com/233cdpns</t>
         </is>
       </c>
     </row>
